--- a/artfynd/A 23151-2026 artfynd.xlsx
+++ b/artfynd/A 23151-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>185129</v>
+        <v>185119</v>
       </c>
       <c r="B2" t="n">
-        <v>93020</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,12 +700,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(With.) Myrin</t>
+          <t>(L. ex Dicks.) Myrin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474744.1976174954</v>
+        <v>474721</v>
       </c>
       <c r="R2" t="n">
-        <v>6330714.532363139</v>
+        <v>6330784</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,24 +757,14 @@
           <t>2007-07-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2007-07-22</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1m från vattnet, 1 tuss</t>
+          <t>2m från vattnet, 2 tussar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,7 +788,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>pors</t>
+          <t>sten</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -821,15 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>185126</v>
+        <v>185122</v>
       </c>
       <c r="B3" t="n">
-        <v>93020</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96313</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -851,12 +831,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(With.) Myrin</t>
+          <t>(L. ex Dicks.) Myrin</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>147</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -875,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474751.9258348462</v>
+        <v>474728</v>
       </c>
       <c r="R3" t="n">
-        <v>6330732.943678522</v>
+        <v>6330759</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -908,24 +888,14 @@
           <t>2007-07-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2007-07-22</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0m från vattnet, 2 tussar</t>
+          <t>1m från vattnet, 19 tussar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -967,15 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>185123</v>
+        <v>185124</v>
       </c>
       <c r="B4" t="n">
-        <v>93020</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96313</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,12 +962,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(With.) Myrin</t>
+          <t>(L. ex Dicks.) Myrin</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1021,10 +986,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474727.6039264246</v>
+        <v>474752</v>
       </c>
       <c r="R4" t="n">
-        <v>6330758.608497257</v>
+        <v>6330733</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1054,24 +1019,14 @@
           <t>2007-07-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2007-07-22</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0m från vattnet, 11 tussar</t>
+          <t>2m från vattnet, 1 tuss</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1110,6 +1065,137 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>185127</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96313</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>530</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Hårklomossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dichelyma capillaceum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L. ex Dicks.) Myrin</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Norra Stråken, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>474744</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6330715</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Aneboda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2007-07-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2007-07-22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1m från vattnet, 13 tussar</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Vattenstrand</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>sjöstrand</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>sten</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23151-2026 artfynd.xlsx
+++ b/artfynd/A 23151-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -803,6 +808,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/185119</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -934,6 +944,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/185122</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1065,6 +1080,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/185124</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1196,8 +1216,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/185127</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>